--- a/homepage-bilingual/全網英文Meta_2026-10-28.xlsx
+++ b/homepage-bilingual/全網英文Meta_2026-10-28.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全網英文 Meta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新紀錄" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全網英文 Meta'!$A$1:$L$259</definedName>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -91,7 +101,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -529,7 +542,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>網站英文產品名狀態</t>
+          <t>狀態（網站英文產品名／英文版）</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -2905,834 +2918,902 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>頁面（商店／Blog 列表）</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>blog</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>Catering Blog | Party &amp; Event Tips | Kitchen AO Hong Kong</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>Guides and ideas for party catering, corporate events, festivals and vegetarian menus in Hong Kong from the Kitchen AO team.</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="I50" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n">
+      <c r="B51" s="6" t="n">
         <v>14128</v>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>到會中伏</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/catering-pitfalls-guide/</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/catering-pitfalls-guide/</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>How to Avoid Catering Mistakes: 5 Pitfalls | Kitchen AO</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>Five common catering pitfalls in Hong Kong and how to avoid them, with expert tips on menus, quantities, delivery and budget.</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="I51" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n">
+      <c r="B52" s="6" t="n">
         <v>14164</v>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>公司活動到會</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/company-event-catering-guide/</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/company-event-catering-guide/</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>Corporate Event Catering Guide 2026 | Budget &amp; Menus</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G52" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Plan corporate event catering in Hong Kong: budget per head, menu ideas, service options and timelines for a professional event.</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="I52" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n">
+      <c r="B53" s="6" t="n">
         <v>14183</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>小朋友生日會</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/kids-birthday-party-catering/</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/kids-birthday-party-catering/</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>Kids Party Food &amp; Children's Party Catering 2026</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>How to choose children's party catering in Hong Kong: kids party food ideas, portions, allergies and party set suggestions.</t>
         </is>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="I53" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
         <is>
           <t>kids party food 110；childrens party catering 90（GSC 37）；childrens party food 40</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n">
+      <c r="B54" s="6" t="n">
         <v>14400</v>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>激光打印食物</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/laser-printed-food-party/</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/laser-printed-food-party/</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>Laser-Printed Party Food | Custom Burgers &amp; Macarons</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G54" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Laser-printed burgers and engraved macarons: a new way to personalise party food and corporate events in Hong Kong.</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="I54" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n">
+      <c r="B55" s="6" t="n">
         <v>14610</v>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>母親節</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/mothers-day-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/mothers-day-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>Mother's Day Catering Offer | Free Handmade Cookies</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G55" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Celebrate Mother's Day with Kitchen AO catering and receive free handmade cookies with your order. Delivered across Hong Kong.</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="I55" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="6" t="n">
         <v>14795</v>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>素食到會</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/vegetarian-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/vegetarian-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <t>Vegetarian Catering Hong Kong 2026 | Party Guide</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>How to cater for vegetarian guests at your party: meat-free menu ideas, labelling tips and vegetarian catering sets in Hong Kong.</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="I56" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n">
+      <c r="B57" s="6" t="n">
         <v>14835</v>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>船河食物</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/boat-party-catering-guide/</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/boat-party-catering-guide/</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>Junk Boat Party Food Checklist 2026 | Kitchen AO</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>Everything you need for a Hong Kong junk boat party: food checklist, quantities, packing tips and free-delivery boat party catering sets.</t>
         </is>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
         <is>
           <t>junk party 110；boat party</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
+      <c r="B58" s="6" t="n">
         <v>15897</v>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>中秋</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/mid-autumn-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/mid-autumn-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <t>Mid-Autumn Festival Catering 2026 | Reunion Sets</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G58" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>Six Mid-Autumn reunion catering sets and corporate mooncakes for family gatherings and company celebrations in Hong Kong.</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="I58" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n">
+      <c r="B59" s="6" t="n">
         <v>16290</v>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>萬聖節</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/halloween-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/halloween-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>Halloween Party Catering 2026 | Party Food Ideas</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G59" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>Halloween party food ideas and catering sets for 2026, plus the story behind Halloween. Spooky party catering delivered across Hong Kong.</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="I59" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B60" s="4" t="n">
+      <c r="B60" s="6" t="n">
         <v>16468</v>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>聖誕</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/christmas-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/christmas-catering-hong-kong/</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>Christmas Catering Hong Kong | Xmas Party Food | Kitchen AO</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="6" t="n">
         <v>59</v>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Christmas catering in Hong Kong: festive party sets and Xmas party food for family gatherings and office Christmas parties, delivered to your door.</t>
         </is>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>christmas catering 90；xmas catering 90；christmas catering hong kong 70；christmas party hong kong 90</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n">
+      <c r="B61" s="6" t="n">
         <v>17646</v>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>團年飯</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/cny-reunion-dinner-guide/</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/cny-reunion-dinner-guide/</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>Chinese New Year Reunion Dinner Guide 2026 | Kitchen AO</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G61" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>Reunion dinner and opening dinner explained: Chinese New Year traditions, lucky dishes and their meanings for 2026.</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
+      <c r="I61" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n">
+      <c r="B62" s="6" t="n">
         <v>18461</v>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>到會邊間好</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/hongkong-catering-2026-e9-a6-99-e6-b8-af-e5-88-b0-e6-9c-83-e9-82-8a-e9-96-93-e5-a5-bd/</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/hongkong-catering-2026-e9-a6-99-e6-b8-af-e5-88-b0-e6-9c-83-e9-82-8a-e9-96-93-e5-a5-bd/</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>Best Catering in Hong Kong 2026 | How to Compare</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G62" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>Which catering service in Hong Kong is best for you? Compare menus, prices, delivery and service with our 2026 checklist.</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
+      <c r="I62" s="6" t="n">
         <v>121</v>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n">
+      <c r="B63" s="6" t="n">
         <v>18495</v>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>公司到會點揀</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/hong-kong-company-catering-how-to-choose/</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/hong-kong-company-catering-how-to-choose/</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>How to Choose Corporate Catering in Hong Kong | Kitchen AO</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G63" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Five key points for choosing quality corporate catering in Hong Kong, from menu variety and food safety to punctual delivery.</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
+      <c r="I63" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B64" s="4" t="n">
+      <c r="B64" s="6" t="n">
         <v>21808</v>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>野餐好去處</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/hong-kong-picnic-spots-picnic-box/</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/hong-kong-picnic-spots-picnic-box/</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <t>Picnic Spots Hong Kong 2026 | 33 Best Parks | Kitchen AO</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>33 picnic spots in Hong Kong with large lawns, sea views and pet-friendly areas, plus parking tips and picnic box ideas.</t>
         </is>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>picnic 2,400</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n">
+      <c r="B65" s="6" t="n">
         <v>21876</v>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>素食種類</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/vegetarian-types-guide/</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/vegetarian-types-guide/</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>Types of Vegetarian Diets Explained | Kitchen AO</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G65" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>Lacto-ovo, five-pungent-free, vegan and plant-based: a clear guide to the types of vegetarian diets common in Hong Kong.</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
+      <c r="I65" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Blog</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n">
+      <c r="B66" s="6" t="n">
         <v>21890</v>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Vegan Vegetarian 中文</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/blog/vegan-vegetarian-meaning/</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>https://aoaodelivery.com/en/blog/vegan-vegetarian-meaning/</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>Vegan vs Vegetarian: Meanings in Chinese | Kitchen AO</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G66" s="6" t="n">
         <v>53</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>What vegan, vegetarian, flexitarian and pescatarian mean, with the Chinese terms used in Hong Kong, Taiwan and the West.</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
+      <c r="I66" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>英文版已停用：/en/blog/ 已 301 至中文版（2026-10-29），此英文 Meta 不再使用</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5848,24 +5929,24 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Crispy Fried Chicken Cartilage with Onion Rings | Kitchen AO</t>
+          <t>Crispy Fried Chicken Cartilage and Onion Rings | Kitchen AO</t>
         </is>
       </c>
       <c r="G109" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Crispy Fried Chicken Cartilage with Onion Rings, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Crispy Fried Chicken Cartilage and Onion Rings, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
-      <c r="K109" s="6" t="inlineStr">
-        <is>
-          <t>⚠ 網站英文名「Fried Squid Tentacles」錯誤：中文名及網址都是雞軟骨（chicken cartilage），Meta 已改用正確名稱，請同時修正網站英文產品名；沿用網站英文名</t>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
@@ -6108,24 +6189,24 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Cheese, Pork Floss &amp; Seafood Croissants | Kitchen AO</t>
+          <t>Cheese Pork Floss &amp; Seafood Croissants | Kitchen AO</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Cheese, Pork Floss &amp; Seafood Croissants, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Cheese Pork Floss &amp; Seafood Croissants, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Cheese, Pork Floss &amp; Seafood Croissants</t>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -6264,24 +6345,24 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Mini Cheese Pork &amp; Beef Burgers | Kitchen AO</t>
+          <t>Mini Hand-Pattied Cheese Burgers | Kitchen AO</t>
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Mini Cheese Pork &amp; Beef Burgers, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Mini Hand-Pattied Cheese Burgers, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J117" s="2" t="inlineStr"/>
-      <c r="K117" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Mini Cheese Pork &amp; Beef Burgers</t>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
@@ -6316,24 +6397,24 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Thai-Style Chilled Chicken Feet | Kitchen AO</t>
+          <t>Thai-Style Hot &amp; Spicy Chicken Feet | Kitchen AO</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Thai-Style Chilled Chicken Feet, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Thai-Style Hot &amp; Spicy Chicken Feet, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J118" s="2" t="inlineStr"/>
-      <c r="K118" s="6" t="inlineStr">
-        <is>
-          <t>⚠ 英文名只有「.」，未有翻譯；網站未有英文名，建議在 TranslatePress 補上：Thai-Style Chilled Chicken Feet</t>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -7252,24 +7333,24 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Kagoshima Honey Herb Char Siu | Kitchen AO</t>
+          <t>Hong Kong-Style Grilled Kagoshima in Herbs and Honey Char Siu Steak</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Kagoshima Honey Herb Char Siu, freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Hong Kong-Style Grilled Kagoshima in Herbs and Honey Char Siu Steak, freshly made by Kitchen AO and delivered across Hong Kong.</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Kagoshima Honey Herb Char Siu</t>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -7824,11 +7905,11 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>AO 35-40pax Refreshment Set | Kitchen AO</t>
+          <t>AO 35-40 pax Refreshment Set | Kitchen AO</t>
         </is>
       </c>
       <c r="G147" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -7839,9 +7920,9 @@
         <v>141</v>
       </c>
       <c r="J147" s="2" t="inlineStr"/>
-      <c r="K147" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 35-40pax Refreshment Set</t>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
@@ -9087,9 +9168,9 @@
         <v>122</v>
       </c>
       <c r="J171" s="2" t="inlineStr"/>
-      <c r="K171" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Three-Tier Silver Food Stand</t>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
@@ -9243,9 +9324,9 @@
         <v>126</v>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Three-Tier Basketball Food Stand</t>
+      <c r="K174" s="7" t="inlineStr">
+        <is>
+          <t>網站未有英文名，建議在 TranslatePress 補上：THREE-TIER BASKETBALL FOOD STAND</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -9399,9 +9480,9 @@
         <v>119</v>
       </c>
       <c r="J177" s="2" t="inlineStr"/>
-      <c r="K177" s="6" t="inlineStr">
-        <is>
-          <t>⚠ 英文名 Dount 拼錯，應為 Doughnut；沿用網站英文名</t>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
@@ -9451,9 +9532,9 @@
         <v>132</v>
       </c>
       <c r="J178" s="2" t="inlineStr"/>
-      <c r="K178" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Yau Dak Gaai Juice Range</t>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
@@ -9971,9 +10052,9 @@
         <v>146</v>
       </c>
       <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Nine Delights Gourmet Canapés Box Lv. 1</t>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
@@ -10023,9 +10104,9 @@
         <v>146</v>
       </c>
       <c r="J189" s="2" t="inlineStr"/>
-      <c r="K189" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Nine Delights Gourmet Canapés Box Lv. 2</t>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
@@ -10075,9 +10156,9 @@
         <v>146</v>
       </c>
       <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Nine Delights Gourmet Canapés Box Lv. 3</t>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
@@ -10595,9 +10676,9 @@
         <v>139</v>
       </c>
       <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Meat Monster Admiral's Harbor Choice Feast Box</t>
+      <c r="K200" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
@@ -10632,24 +10713,24 @@
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>Meat Monster Admiral's Harbor Choice Jumbo Feast Box</t>
+          <t>Meat Monster Admiral's Harbor Mega Feast Box | Kitchen AO</t>
         </is>
       </c>
       <c r="G201" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Meat Monster Admiral's Harbor Choice Jumbo Feast Box: roasts and grilled meats for meat-loving parties, delivered across Hong Kong by Kitchen AO.</t>
+          <t>Meat Monster Admiral's Harbor Mega Feast Box: roasts and grilled meats for meat-loving parties, delivered across Hong Kong by Kitchen AO.</t>
         </is>
       </c>
       <c r="I201" s="2" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="J201" s="2" t="inlineStr"/>
-      <c r="K201" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Meat Monster Admiral's Harbor Choice Jumbo Feast Box</t>
+      <c r="K201" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
@@ -10907,9 +10988,9 @@
         <v>130</v>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 100pax Centenary Celebration Party Set</t>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>網站未有英文名，建議在 TranslatePress 補上：AO 100PAX CENTENARY CELEBRATION PARTY SET</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -11323,9 +11404,9 @@
         <v>99</v>
       </c>
       <c r="J214" s="2" t="inlineStr"/>
-      <c r="K214" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Creamed Spinach</t>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L214" s="2" t="inlineStr">
@@ -11375,9 +11456,9 @@
         <v>133</v>
       </c>
       <c r="J215" s="2" t="inlineStr"/>
-      <c r="K215" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Japanese Stir-Fried Vegetables with Sakura Shrimp</t>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L215" s="2" t="inlineStr">
@@ -11427,9 +11508,9 @@
         <v>106</v>
       </c>
       <c r="J216" s="2" t="inlineStr"/>
-      <c r="K216" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Creamy Mashed Potatoes</t>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L216" s="2" t="inlineStr">
@@ -11479,9 +11560,9 @@
         <v>108</v>
       </c>
       <c r="J217" s="2" t="inlineStr"/>
-      <c r="K217" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Garlic Sautéed Courgette</t>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L217" s="2" t="inlineStr">
@@ -11531,9 +11612,9 @@
         <v>106</v>
       </c>
       <c r="J218" s="2" t="inlineStr"/>
-      <c r="K218" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Honey Butter Sweetcorn</t>
+      <c r="K218" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L218" s="2" t="inlineStr">
@@ -11583,9 +11664,9 @@
         <v>109</v>
       </c>
       <c r="J219" s="2" t="inlineStr"/>
-      <c r="K219" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Foil-Baked Sweet Potatoes</t>
+      <c r="K219" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L219" s="2" t="inlineStr">
@@ -11635,9 +11716,9 @@
         <v>113</v>
       </c>
       <c r="J220" s="2" t="inlineStr"/>
-      <c r="K220" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Goji Leaves in Superior Broth</t>
+      <c r="K220" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
@@ -12311,9 +12392,9 @@
         <v>138</v>
       </c>
       <c r="J233" s="2" t="inlineStr"/>
-      <c r="K233" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Vita Unsweetened Cold Brew Tea</t>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L233" s="2" t="inlineStr">
@@ -12400,24 +12481,24 @@
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>Sake Crab Roe &amp; Flounder Claypot Rice (4 lb) | Kitchen AO</t>
+          <t>Sharaku Sake-Braised Crab Roe &amp; Seared Flounder Claypot Rice</t>
         </is>
       </c>
       <c r="G235" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Sake Crab Roe &amp; Flounder Claypot Rice (4 lb), freshly made by Kitchen AO for parties and corporate events. Order online with delivery across Hong Kong.</t>
+          <t>Sharaku Sake-Braised Crab Roe &amp; Seared Flounder Claypot Rice, freshly made by Kitchen AO and delivered across Hong Kong.</t>
         </is>
       </c>
       <c r="I235" s="2" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="J235" s="2" t="inlineStr"/>
-      <c r="K235" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Sake Crab Roe &amp; Flounder Claypot Rice (4 lb)</t>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L235" s="2" t="inlineStr">
@@ -12467,9 +12548,9 @@
         <v>128</v>
       </c>
       <c r="J236" s="2" t="inlineStr"/>
-      <c r="K236" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Wagyu &amp; Wild Mushroom Skewer</t>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L236" s="2" t="inlineStr">
@@ -12519,9 +12600,9 @@
         <v>135</v>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
-      <c r="K237" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Dill Smoked Salmon &amp; Asparagus Roll</t>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L237" s="2" t="inlineStr">
@@ -12571,9 +12652,9 @@
         <v>139</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Ratatouille Chicken &amp; Tomato Bread Roll</t>
+      <c r="K238" s="7" t="inlineStr">
+        <is>
+          <t>網站未有英文名，建議在 TranslatePress 補上：RATATOUILLE CHICKEN &amp; TOMATO BREAD ROLL</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
@@ -12623,9 +12704,9 @@
         <v>140</v>
       </c>
       <c r="J239" s="2" t="inlineStr"/>
-      <c r="K239" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Sous-Vide Chicken &amp; Ratatouille Sandwich</t>
+      <c r="K239" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L239" s="2" t="inlineStr">
@@ -12675,9 +12756,9 @@
         <v>122</v>
       </c>
       <c r="J240" s="2" t="inlineStr"/>
-      <c r="K240" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Lemon Dill Prawn Blini</t>
+      <c r="K240" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L240" s="2" t="inlineStr">
@@ -12727,9 +12808,9 @@
         <v>151</v>
       </c>
       <c r="J241" s="2" t="inlineStr"/>
-      <c r="K241" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Foie Gras Mousse with Pistachio Cookie &amp; Lime Jelly</t>
+      <c r="K241" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L241" s="2" t="inlineStr">
@@ -12779,9 +12860,9 @@
         <v>141</v>
       </c>
       <c r="J242" s="2" t="inlineStr"/>
-      <c r="K242" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Seared Scallop, Taro &amp; Red Cabbage Skewer</t>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L242" s="2" t="inlineStr">
@@ -12831,9 +12912,9 @@
         <v>134</v>
       </c>
       <c r="J243" s="2" t="inlineStr"/>
-      <c r="K243" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Roast Duck, Cucumber &amp; Garlic Roll</t>
+      <c r="K243" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L243" s="2" t="inlineStr">
@@ -12883,9 +12964,9 @@
         <v>126</v>
       </c>
       <c r="J244" s="2" t="inlineStr"/>
-      <c r="K244" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Fig &amp; Duck Breast Crostini</t>
+      <c r="K244" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L244" s="2" t="inlineStr">
@@ -12935,9 +13016,9 @@
         <v>138</v>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Smoked Salmon &amp; Avocado Baguette Toast</t>
+      <c r="K245" s="7" t="inlineStr">
+        <is>
+          <t>網站未有英文名，建議在 TranslatePress 補上：SMOKED SALMON &amp; AVOCADO BAGUETTE TOAST</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
@@ -12987,9 +13068,9 @@
         <v>133</v>
       </c>
       <c r="J246" s="2" t="inlineStr"/>
-      <c r="K246" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Smoked Duck, Chestnut &amp; Pear Tart</t>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L246" s="2" t="inlineStr">
@@ -13039,9 +13120,9 @@
         <v>134</v>
       </c>
       <c r="J247" s="2" t="inlineStr"/>
-      <c r="K247" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：Teriyaki Chicken Roll with Avocado</t>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L247" s="2" t="inlineStr">
@@ -13091,9 +13172,9 @@
         <v>136</v>
       </c>
       <c r="J248" s="2" t="inlineStr"/>
-      <c r="K248" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 5-6pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K248" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L248" s="2" t="inlineStr">
@@ -13143,9 +13224,9 @@
         <v>138</v>
       </c>
       <c r="J249" s="2" t="inlineStr"/>
-      <c r="K249" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 8-10pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L249" s="2" t="inlineStr">
@@ -13195,9 +13276,9 @@
         <v>140</v>
       </c>
       <c r="J250" s="2" t="inlineStr"/>
-      <c r="K250" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 12-16pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L250" s="2" t="inlineStr">
@@ -13247,9 +13328,9 @@
         <v>140</v>
       </c>
       <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 18-22pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L251" s="2" t="inlineStr">
@@ -13299,9 +13380,9 @@
         <v>140</v>
       </c>
       <c r="J252" s="2" t="inlineStr"/>
-      <c r="K252" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 26-30pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L252" s="2" t="inlineStr">
@@ -13351,9 +13432,9 @@
         <v>140</v>
       </c>
       <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="6" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 35-40pax Mid-Autumn Reunion Set 2026</t>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>沿用：中秋產品網站英文名不更改（Meta 用建議英文名）</t>
         </is>
       </c>
       <c r="L253" s="2" t="inlineStr">
@@ -14196,4 +14277,118 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>更新內容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A 匯入：頁面、Blog、產品分類英文 Meta（103 項）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B 匯入：產品英文 Meta（155 項）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B2：產品英文 Title 加「| Kitchen AO」（128 項；超過 60 字元的不加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B3：8 個產品 Title／Description 跟網站手動修改的英文名（6063、6072、6077、6078、6274、6409、14306、19579）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>舊 EN SEO snippet 停用；全站英文 Meta 由「中英文版通用工具 v2」English SEO 方格提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blog 只保留中文版：TranslatePress 排除 /blog/、/blog/*；Rank Math 301 ^en/blog(/.*)?$ → /blog$1（灰色列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>紅色＝網站英文產品名仍是中文或中英混雜，待補：10388、14342、20217、20225</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/homepage-bilingual/全網英文Meta_2026-10-28.xlsx
+++ b/homepage-bilingual/全網英文Meta_2026-10-28.xlsx
@@ -46,7 +46,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -68,11 +68,6 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAD4D4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,9 +97,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -9324,9 +9316,9 @@
         <v>126</v>
       </c>
       <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="7" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：THREE-TIER BASKETBALL FOOD STAND</t>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
@@ -10988,9 +10980,9 @@
         <v>130</v>
       </c>
       <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="7" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：AO 100PAX CENTENARY CELEBRATION PARTY SET</t>
+      <c r="K206" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L206" s="2" t="inlineStr">
@@ -12652,9 +12644,9 @@
         <v>139</v>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
-      <c r="K238" s="7" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：RATATOUILLE CHICKEN &amp; TOMATO BREAD ROLL</t>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
@@ -13016,9 +13008,9 @@
         <v>138</v>
       </c>
       <c r="J245" s="2" t="inlineStr"/>
-      <c r="K245" s="7" t="inlineStr">
-        <is>
-          <t>網站未有英文名，建議在 TranslatePress 補上：SMOKED SALMON &amp; AVOCADO BAGUETTE TOAST</t>
+      <c r="K245" s="2" t="inlineStr">
+        <is>
+          <t>沿用網站英文名</t>
         </is>
       </c>
       <c r="L245" s="2" t="inlineStr">
@@ -14379,12 +14371,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>紅色＝網站英文產品名仍是中文或中英混雜，待補：10388、14342、20217、20225</t>
+          <t>網站已補 4 個英文產品名：10388、14342、20217、20225（與 Meta 一致，毋須重新匯入）；全部產品已有英文名</t>
         </is>
       </c>
     </row>
